--- a/5S_API/5S.API/Template/KetQuaChamDiem.xlsx
+++ b/5S_API/5S.API/Template/KetQuaChamDiem.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D2S project\5S_PLX\5S_API\5S.API\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuAn\5S\5S_PLX\5S_API\5S.API\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FFB5BF-94A5-4028-8049-D607FA16855A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AC6732-E1B0-468C-AA84-156677F67222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DAC2155-505B-469C-82C9-A9FEAF155253}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{4DAC2155-505B-469C-82C9-A9FEAF155253}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>STT</t>
   </si>
@@ -33,16 +33,21 @@
     <t>Tên đơn vị</t>
   </si>
   <si>
-    <t>Số lần chấm điểm</t>
-  </si>
-  <si>
-    <t>Điểm bình quân</t>
-  </si>
-  <si>
     <t>Xếp loại</t>
   </si>
   <si>
     <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Điểm 
+bình quân</t>
+  </si>
+  <si>
+    <t>Số lần 
+chấm điểm</t>
+  </si>
+  <si>
+    <t>Điểm từng lần chấm</t>
   </si>
 </sst>
 </file>
@@ -100,10 +105,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -123,9 +134,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -163,7 +174,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -269,7 +280,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -411,7 +422,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -419,34 +430,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CD819C-8F76-4102-AD04-2DCBA9644486}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="13.33203125" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.21875" customWidth="1"/>
-    <col min="3" max="3" width="44.5546875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
-    <col min="5" max="5" width="53.21875" customWidth="1"/>
-    <col min="6" max="6" width="59.5546875" customWidth="1"/>
+    <col min="2" max="2" width="41.77734375" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="55.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="48.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
